--- a/data/trans_camb/P1801_2016_2023-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1801_2016_2023-Provincia-trans_camb.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>15,06</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,94</t>
+          <t>16,39</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 27,1</t>
+          <t>6,51; 23,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 25,51</t>
+          <t>9,89; 24,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 23,56</t>
+          <t>10,76; 21,99</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 60,84</t>
+          <t>12,5; 54,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,57; 53,81</t>
+          <t>17,24; 51,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,18; 49,4</t>
+          <t>19,89; 46,11</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-21,99</t>
+          <t>-21,64</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-27,53</t>
+          <t>-28,24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-24,89</t>
+          <t>-25,02</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,36; -16,34</t>
+          <t>-28,06; -15,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-32,78; -21,54</t>
+          <t>-33,99; -22,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,28; -20,65</t>
+          <t>-29,19; -20,75</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-47,07%</t>
+          <t>-46,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-47,64%</t>
+          <t>-48,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-47,53%</t>
+          <t>-47,78%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,02; -36,61</t>
+          <t>-56,95; -34,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,08; -38,31</t>
+          <t>-55,79; -40,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,78; -41,09</t>
+          <t>-53,92; -41,41</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22,18</t>
+          <t>22,17</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,71</t>
+          <t>12,74</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,88</t>
+          <t>17,38</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,94; 29,31</t>
+          <t>14,65; 30,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 20,64</t>
+          <t>5,95; 19,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,41; 22,98</t>
+          <t>12,37; 22,27</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,17; 74,55</t>
+          <t>30,16; 76,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,89; 40,51</t>
+          <t>9,91; 38,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,95; 49,26</t>
+          <t>23,51; 48,2</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-3,58</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-19,28</t>
+          <t>-8,0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-12,46</t>
+          <t>-6,68</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 5,57</t>
+          <t>-12,99; 3,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-36,67; -8,15</t>
+          <t>-14,46; -0,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,0; -4,24</t>
+          <t>-12,1; -0,84</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-6,48%</t>
+          <t>-9,89%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-31,3%</t>
+          <t>-12,98%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-21,31%</t>
+          <t>-11,43%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 10,98</t>
+          <t>-22,53; 6,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,67; -14,0</t>
+          <t>-22,48; -1,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,73; -7,53</t>
+          <t>-20,19; -1,53</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13,47</t>
+          <t>10,1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13,67</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>11,3</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 23,61</t>
+          <t>1,27; 19,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,77; 21,82</t>
+          <t>3,7; 20,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,87; 20,73</t>
+          <t>5,25; 17,38</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,24; 58,78</t>
+          <t>2,48; 47,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9,64; 43,72</t>
+          <t>6,32; 43,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,33; 44,75</t>
+          <t>9,68; 37,18</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>7,44</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>8,98</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>8,08</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,11; 17,1</t>
+          <t>0,09; 15,84</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,41; 16,93</t>
+          <t>1,55; 16,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,21; 14,65</t>
+          <t>2,48; 14,02</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,13; 35,34</t>
+          <t>0,18; 33,82</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2,19; 30,95</t>
+          <t>2,49; 30,31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5,65; 28,57</t>
+          <t>4,28; 27,02</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>25,51</t>
+          <t>24,02</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>21,55</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27,87</t>
+          <t>22,81</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>19,16; 31,62</t>
+          <t>18,46; 29,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19,26; 41,22</t>
+          <t>16,3; 26,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21,5; 39,6</t>
+          <t>18,94; 26,61</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>49,95; 95,59</t>
+          <t>48,44; 90,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>38,14; 92,77</t>
+          <t>31,16; 58,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49,39; 97,93</t>
+          <t>42,13; 66,09</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>-17,71</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-19,8</t>
+          <t>-20,39</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-9,24</t>
+          <t>-19,14</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 27,39</t>
+          <t>-22,78; -12,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-24,54; -14,86</t>
+          <t>-24,87; -16,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 10,73</t>
+          <t>-22,17; -15,48</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>-35,15%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-31,43%</t>
+          <t>-32,38%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-16,24%</t>
+          <t>-33,65%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 56,31</t>
+          <t>-43,01; -26,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-37,39; -24,74</t>
+          <t>-38,09; -26,47</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-33,72; 19,01</t>
+          <t>-38,03; -28,33</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,56</t>
+          <t>-1,28; 4,09</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 8,18</t>
+          <t>-3,51; 1,12</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 9,28</t>
+          <t>-1,6; 1,76</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-0,02%</t>
+          <t>-2,11%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3,85; 36,71</t>
+          <t>-2,61; 9,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 14,48</t>
+          <t>-5,98; 2,03</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 18,12</t>
+          <t>-3,04; 3,45</t>
         </is>
       </c>
     </row>
